--- a/data/historico/semana_320.xlsx
+++ b/data/historico/semana_320.xlsx
@@ -5259,7 +5259,7 @@
       </c>
       <c r="B8" s="38" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="C8" s="38" t="inlineStr">
